--- a/data/experiment2_final_choice_conflict.xlsx
+++ b/data/experiment2_final_choice_conflict.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marta\Nextcloud\Shared_SweetC\Experiments\ExpPrefer\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C768DE-3BD5-49A2-B63D-44F35F4336BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6204012C-0AC8-48B3-BD49-767BCA0766C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FinalSliderResponses" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="7">
   <si>
     <t>Response</t>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t>Medium</t>
+  </si>
+  <si>
+    <t>Count</t>
   </si>
 </sst>
 </file>
@@ -96,12 +99,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -408,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.90625" customWidth="1"/>
@@ -416,8 +416,8 @@
     <col min="3" max="3" width="11.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -426,8 +426,11 @@
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -437,8 +440,11 @@
       <c r="C2">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -448,8 +454,11 @@
       <c r="C3">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -459,8 +468,11 @@
       <c r="C4">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -470,8 +482,11 @@
       <c r="C5">
         <v>29</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -481,8 +496,11 @@
       <c r="C6">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -492,8 +510,11 @@
       <c r="C7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -503,8 +524,11 @@
       <c r="C8">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -514,8 +538,11 @@
       <c r="C9">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -525,8 +552,11 @@
       <c r="C10">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -536,8 +566,11 @@
       <c r="C11">
         <v>30</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -547,8 +580,11 @@
       <c r="C12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -558,8 +594,11 @@
       <c r="C13">
         <v>30</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -569,8 +608,11 @@
       <c r="C14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -580,8 +622,11 @@
       <c r="C15">
         <v>30</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -591,8 +636,11 @@
       <c r="C16">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -602,8 +650,11 @@
       <c r="C17">
         <v>30</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -613,8 +664,11 @@
       <c r="C18">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -624,8 +678,11 @@
       <c r="C19">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -635,8 +692,11 @@
       <c r="C20">
         <v>10</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -646,8 +706,11 @@
       <c r="C21">
         <v>24</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -657,8 +720,11 @@
       <c r="C22">
         <v>30</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -668,8 +734,11 @@
       <c r="C23">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -679,8 +748,11 @@
       <c r="C24">
         <v>30</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -690,8 +762,11 @@
       <c r="C25">
         <v>29</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -701,8 +776,11 @@
       <c r="C26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -712,8 +790,11 @@
       <c r="C27">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -723,8 +804,11 @@
       <c r="C28">
         <v>25</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -734,8 +818,11 @@
       <c r="C29">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -745,8 +832,11 @@
       <c r="C30">
         <v>30</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -756,8 +846,11 @@
       <c r="C31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -767,8 +860,11 @@
       <c r="C32">
         <v>26</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -778,8 +874,11 @@
       <c r="C33">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -789,8 +888,11 @@
       <c r="C34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -800,8 +902,11 @@
       <c r="C35">
         <v>22</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -811,8 +916,11 @@
       <c r="C36">
         <v>22</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -822,8 +930,11 @@
       <c r="C37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -833,8 +944,11 @@
       <c r="C38">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -844,8 +958,11 @@
       <c r="C39">
         <v>25</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -855,8 +972,11 @@
       <c r="C40">
         <v>15</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -866,8 +986,11 @@
       <c r="C41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -877,8 +1000,11 @@
       <c r="C42">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -888,8 +1014,11 @@
       <c r="C43">
         <v>29</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -899,8 +1028,11 @@
       <c r="C44">
         <v>14</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -910,8 +1042,11 @@
       <c r="C45">
         <v>15</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -921,8 +1056,11 @@
       <c r="C46">
         <v>20</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -932,8 +1070,11 @@
       <c r="C47">
         <v>11</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -943,8 +1084,11 @@
       <c r="C48">
         <v>15</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -954,8 +1098,11 @@
       <c r="C49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -965,8 +1112,11 @@
       <c r="C50">
         <v>20</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -976,8 +1126,11 @@
       <c r="C51">
         <v>14</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -987,8 +1140,11 @@
       <c r="C52">
         <v>22</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -998,8 +1154,11 @@
       <c r="C53">
         <v>10</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1009,8 +1168,11 @@
       <c r="C54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1020,8 +1182,11 @@
       <c r="C55">
         <v>5</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1031,8 +1196,11 @@
       <c r="C56">
         <v>17</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1042,8 +1210,11 @@
       <c r="C57">
         <v>14</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1053,8 +1224,11 @@
       <c r="C58">
         <v>30</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1064,8 +1238,11 @@
       <c r="C59">
         <v>30</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1075,8 +1252,11 @@
       <c r="C60">
         <v>30</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1086,8 +1266,11 @@
       <c r="C61">
         <v>30</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1097,8 +1280,11 @@
       <c r="C62">
         <v>30</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1108,8 +1294,11 @@
       <c r="C63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1119,8 +1308,11 @@
       <c r="C64">
         <v>30</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1130,8 +1322,11 @@
       <c r="C65">
         <v>28</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1141,8 +1336,11 @@
       <c r="C66">
         <v>29</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1152,8 +1350,11 @@
       <c r="C67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1163,8 +1364,11 @@
       <c r="C68">
         <v>24</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1174,8 +1378,11 @@
       <c r="C69">
         <v>16</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1185,8 +1392,11 @@
       <c r="C70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1196,8 +1406,11 @@
       <c r="C71">
         <v>30</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1207,8 +1420,11 @@
       <c r="C72">
         <v>30</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1218,8 +1434,11 @@
       <c r="C73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -1229,8 +1448,11 @@
       <c r="C74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -1240,8 +1462,11 @@
       <c r="C75">
         <v>26</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -1251,8 +1476,11 @@
       <c r="C76">
         <v>30</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -1262,8 +1490,11 @@
       <c r="C77">
         <v>19</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -1273,8 +1504,11 @@
       <c r="C78">
         <v>27</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -1284,8 +1518,11 @@
       <c r="C79">
         <v>30</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -1295,8 +1532,11 @@
       <c r="C80">
         <v>29</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -1306,8 +1546,11 @@
       <c r="C81">
         <v>22</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
@@ -1317,8 +1560,11 @@
       <c r="C82">
         <v>22</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -1328,8 +1574,11 @@
       <c r="C83">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
@@ -1339,8 +1588,11 @@
       <c r="C84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
@@ -1350,8 +1602,11 @@
       <c r="C85">
         <v>11</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
@@ -1361,8 +1616,11 @@
       <c r="C86">
         <v>30</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -1372,8 +1630,11 @@
       <c r="C87">
         <v>30</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
@@ -1383,8 +1644,11 @@
       <c r="C88">
         <v>19</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
@@ -1394,8 +1658,11 @@
       <c r="C89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
@@ -1405,8 +1672,11 @@
       <c r="C90">
         <v>15</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
@@ -1416,8 +1686,11 @@
       <c r="C91">
         <v>29</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
@@ -1427,8 +1700,11 @@
       <c r="C92">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
@@ -1438,8 +1714,11 @@
       <c r="C93">
         <v>26</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -1449,8 +1728,11 @@
       <c r="C94">
         <v>23</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
@@ -1460,8 +1742,11 @@
       <c r="C95">
         <v>30</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
@@ -1471,8 +1756,11 @@
       <c r="C96">
         <v>30</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
@@ -1482,8 +1770,11 @@
       <c r="C97">
         <v>22</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
@@ -1493,8 +1784,11 @@
       <c r="C98">
         <v>30</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
@@ -1504,8 +1798,11 @@
       <c r="C99">
         <v>23</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
@@ -1515,8 +1812,11 @@
       <c r="C100">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
@@ -1526,8 +1826,14 @@
       <c r="C101">
         <v>30</v>
       </c>
+      <c r="D101">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D101">
+    <sortCondition ref="A2:A101"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>